--- a/Progress/Company wise/google/google_prep_questions.xlsx
+++ b/Progress/Company wise/google/google_prep_questions.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Not Done</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tarjan's bridges</t>
+          <t>Graph / Bridges / Tarjan's Low-Link (Undirected)</t>
         </is>
       </c>
     </row>
@@ -3924,6 +3924,134 @@
       <c r="G98" t="inlineStr">
         <is>
           <t>Game Theory / Bitmask DP / Memoized Search</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1.13 Interactive Problems</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Find in Mountain Array</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>1095</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Binary Search / Interactive / Bitonic Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1.17 Geometry - Advanced</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Erect the Fence</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Geometry / Convex Hull / Andrew's Monotone Chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>1.14 Advanced Graph</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Valid Arrangement of Pairs</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2097</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Graph / Eulerian Path / Hierholzer's Algorithm</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1.14 Advanced Graph</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Longest Cycle in a Graph</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Graph / Functional Graph / Cycle Detection (Simplified Tarjan)</t>
         </is>
       </c>
     </row>

--- a/Progress/Company wise/google/google_prep_questions.xlsx
+++ b/Progress/Company wise/google/google_prep_questions.xlsx
@@ -1142,7 +1142,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Not Done</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Not Done</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Not Done</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Not Done</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
